--- a/data/gravel/Van Rysel AF 2025.xlsx
+++ b/data/gravel/Van Rysel AF 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293E61E8-2831-9743-9453-636A1F65E4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8AA59B4-7015-BC4B-8016-3DA7DE874603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1540" yWindow="500" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -320,9 +320,6 @@
     <t>Van Rysel</t>
   </si>
   <si>
-    <t>AF</t>
-  </si>
-  <si>
     <t>aluminum</t>
   </si>
   <si>
@@ -351,6 +348,9 @@
   </si>
   <si>
     <t>frame size</t>
+  </si>
+  <si>
+    <t>GRVL AF</t>
   </si>
 </sst>
 </file>
@@ -774,7 +774,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -798,7 +798,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -806,7 +806,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -814,22 +814,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="E8" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="F8" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -1359,7 +1359,7 @@
         <v>67</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -1385,7 +1385,7 @@
         <v>31</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>

--- a/data/gravel/Van Rysel AF 2025.xlsx
+++ b/data/gravel/Van Rysel AF 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8AA59B4-7015-BC4B-8016-3DA7DE874603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B95638-FA53-E94B-B2AD-180FB7111D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1540" yWindow="500" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>GRVL AF</t>
+  </si>
+  <si>
+    <t>https://www.vanryselus.com/cdn/shop/files/USAGRVLAFGRXBLACKCNFRPE25-8929130-001---Expireson10-12-2033.jpg?v=1738360494&amp;width=1296</t>
   </si>
 </sst>
 </file>
@@ -801,6 +804,11 @@
         <v>97</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Van Rysel AF 2025.xlsx
+++ b/data/gravel/Van Rysel AF 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B95638-FA53-E94B-B2AD-180FB7111D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D79B5E-598D-464B-9964-46F68673A6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1540" yWindow="500" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9660" yWindow="1040" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -260,9 +260,6 @@
     <t>bb_height</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>gravel</t>
   </si>
   <si>
@@ -354,6 +351,15 @@
   </si>
   <si>
     <t>https://www.vanryselus.com/cdn/shop/files/USAGRVLAFGRXBLACKCNFRPE25-8929130-001---Expireson10-12-2033.jpg?v=1738360494&amp;width=1296</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Lille, France</t>
   </si>
 </sst>
 </file>
@@ -757,7 +763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -769,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -777,7 +783,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -801,12 +807,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -814,7 +820,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -822,22 +828,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="E8" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="F8" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -845,7 +851,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9" s="10">
         <v>530</v>
@@ -868,7 +874,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="10">
         <v>450</v>
@@ -892,7 +898,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" s="10">
         <v>115</v>
@@ -916,7 +922,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C12" s="10">
         <v>396</v>
@@ -940,7 +946,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C13" s="10">
         <v>45</v>
@@ -964,7 +970,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14" s="10">
         <v>67</v>
@@ -988,7 +994,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C15" s="10">
         <v>372</v>
@@ -1012,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" s="10">
         <v>535</v>
@@ -1036,7 +1042,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C17" s="10">
         <v>435</v>
@@ -1060,7 +1066,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C18" s="10">
         <v>1020</v>
@@ -1084,7 +1090,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C19" s="10">
         <v>73.5</v>
@@ -1108,7 +1114,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C20" s="10">
         <v>70</v>
@@ -1331,19 +1337,19 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C34" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="E34" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="F34" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="G34" s="9" t="s">
         <v>80</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
@@ -1359,7 +1365,7 @@
         <v>66</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
@@ -1367,7 +1373,7 @@
         <v>67</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -1393,7 +1399,7 @@
         <v>31</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -1613,7 +1619,15 @@
         <v>65</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>75</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Van Rysel AF 2025.xlsx
+++ b/data/gravel/Van Rysel AF 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D79B5E-598D-464B-9964-46F68673A6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693F1B5E-D83A-EC46-B920-2272DEA5EB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9660" yWindow="1040" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1540" yWindow="1040" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,24 @@
   </si>
   <si>
     <t>Lille, France</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -763,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1471,162 +1489,192 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>42</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="1">
-        <v>27.2</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B58" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" s="1">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
+      </c>
+      <c r="B69" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="B70" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71" s="1">
-        <v>1399</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>108</v>
       </c>
     </row>
